--- a/sipii_caixa_20260615.xlsx
+++ b/sipii_caixa_20260615.xlsx
@@ -822,43 +822,185 @@
           <t>https://www.caixa.gov.br/fundos-investimento/renda-fixa/fi-renda-fixa-simples-lp/</t>
         </is>
       </c>
-      <c r="L2" s="2" t="inlineStr"/>
-      <c r="M2" s="2" t="inlineStr"/>
-      <c r="N2" s="2" t="inlineStr"/>
-      <c r="O2" s="2" t="inlineStr"/>
-      <c r="P2" s="2" t="inlineStr"/>
-      <c r="Q2" s="2" t="inlineStr"/>
-      <c r="R2" s="2" t="inlineStr"/>
-      <c r="S2" s="2" t="inlineStr"/>
-      <c r="T2" s="2" t="inlineStr"/>
-      <c r="U2" s="2" t="inlineStr"/>
-      <c r="V2" s="2" t="inlineStr"/>
-      <c r="W2" s="2" t="inlineStr"/>
-      <c r="X2" s="2" t="inlineStr"/>
-      <c r="Y2" s="2" t="inlineStr"/>
-      <c r="Z2" s="2" t="inlineStr"/>
-      <c r="AA2" s="2" t="inlineStr"/>
-      <c r="AB2" s="2" t="inlineStr"/>
-      <c r="AC2" s="2" t="inlineStr"/>
-      <c r="AD2" s="2" t="inlineStr"/>
-      <c r="AE2" s="2" t="inlineStr"/>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>22.791.329/0001-50</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>5980</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>Conservador</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="P2" s="2" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="Q2" s="2" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="R2" s="2" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="S2" s="2" t="inlineStr">
+        <is>
+          <t>0.02</t>
+        </is>
+      </c>
+      <c r="T2" s="2" t="inlineStr">
+        <is>
+          <t>D+0 (du)</t>
+        </is>
+      </c>
+      <c r="U2" s="2" t="inlineStr">
+        <is>
+          <t>D+0 (du)</t>
+        </is>
+      </c>
+      <c r="V2" s="2" t="inlineStr">
+        <is>
+          <t>D+00 (du)</t>
+        </is>
+      </c>
+      <c r="W2" s="2" t="inlineStr">
+        <is>
+          <t>SELIC</t>
+        </is>
+      </c>
+      <c r="X2" s="2" t="inlineStr">
+        <is>
+          <t>RF Simples até 49% Crédito Privado</t>
+        </is>
+      </c>
+      <c r="Y2" s="2" t="inlineStr">
+        <is>
+          <t>Aberto para captação</t>
+        </is>
+      </c>
+      <c r="Z2" s="2" t="inlineStr">
+        <is>
+          <t>LONGO PRAZO</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
+          <t>GERAL</t>
+        </is>
+      </c>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="AC2" s="2" t="inlineStr">
+        <is>
+          <t>17h00</t>
+        </is>
+      </c>
+      <c r="AD2" s="2" t="inlineStr">
+        <is>
+          <t>Não se aplica</t>
+        </is>
+      </c>
+      <c r="AE2" s="2" t="inlineStr">
+        <is>
+          <t>NÃO SE APLICA</t>
+        </is>
+      </c>
       <c r="AF2" s="2" t="inlineStr"/>
-      <c r="AG2" s="2" t="inlineStr"/>
-      <c r="AH2" s="2" t="inlineStr"/>
-      <c r="AI2" s="2" t="inlineStr"/>
-      <c r="AJ2" s="2" t="inlineStr"/>
+      <c r="AG2" s="2" t="inlineStr">
+        <is>
+          <t>["Institucional", "Pessoa Física", "PJ Atacado", "PJ Varejo", "Private"]</t>
+        </is>
+      </c>
+      <c r="AH2" s="2" t="inlineStr">
+        <is>
+          <t>["Institucional", "Pessoa Física", "PJ Atacado", "PJ Varejo", "Private"]</t>
+        </is>
+      </c>
+      <c r="AI2" s="2" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+      <c r="AJ2" s="2" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
       <c r="AK2" s="2" t="inlineStr"/>
-      <c r="AL2" s="2" t="inlineStr"/>
-      <c r="AM2" s="2" t="inlineStr"/>
-      <c r="AN2" s="2" t="inlineStr"/>
-      <c r="AO2" s="2" t="inlineStr"/>
-      <c r="AP2" s="2" t="inlineStr"/>
-      <c r="AQ2" s="2" t="inlineStr"/>
-      <c r="AR2" s="2" t="inlineStr"/>
-      <c r="AS2" s="2" t="inlineStr"/>
-      <c r="AT2" s="2" t="inlineStr"/>
-      <c r="AU2" s="2" t="inlineStr"/>
-      <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AL2" s="2" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="AM2" s="2" t="inlineStr">
+        <is>
+          <t>CAIXA E-SIMPLES FUNDO DE INVESTIMENTO FINANCEIRO RENDA FIXA LONGO PRAZO - RESPONSABILIDADE LIMITADA</t>
+        </is>
+      </c>
+      <c r="AN2" s="2" t="inlineStr">
+        <is>
+          <t>Fundo com movimentação exclusiva pelo IBC/APP.
+OBS: O Fundo possui a funcionalidade de Resgate Automático em caso de adesão pelo cotista, o gerente deverá proceder à contratação no SIART. Para ativar a funcionalidade de Resgate Automático, acessar o SIART -&gt; Movimentação Automática -&gt; Marcar
+As regras da funcionalidade de Movimentação Automática estão descritas no MN TE099.</t>
+        </is>
+      </c>
+      <c r="AO2" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_5980.pdf</t>
+        </is>
+      </c>
+      <c r="AP2" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_5980.pdf</t>
+        </is>
+      </c>
+      <c r="AQ2" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_5980.pdf</t>
+        </is>
+      </c>
+      <c r="AR2" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/COM_5980.pdf</t>
+        </is>
+      </c>
+      <c r="AS2" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_5980.pdf</t>
+        </is>
+      </c>
+      <c r="AT2" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_5980.pdf</t>
+        </is>
+      </c>
+      <c r="AU2" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-termos-adesao/TA_5980.pdf</t>
+        </is>
+      </c>
+      <c r="AV2" s="2" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/caixa-asset/sumario-remuneracao/Documents/sumarios/5980-SUMARIO.pdf</t>
+        </is>
+      </c>
       <c r="AW2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
@@ -13613,44 +13755,192 @@
           <t>https://www.caixa.gov.br/fundos-investimento/multimercado/fi-multimercado-rv30-longo-prazo</t>
         </is>
       </c>
-      <c r="L57" s="4" t="inlineStr"/>
-      <c r="M57" s="4" t="inlineStr"/>
-      <c r="N57" s="4" t="inlineStr"/>
-      <c r="O57" s="4" t="inlineStr"/>
-      <c r="P57" s="4" t="inlineStr"/>
-      <c r="Q57" s="4" t="inlineStr"/>
-      <c r="R57" s="4" t="inlineStr"/>
-      <c r="S57" s="4" t="inlineStr"/>
-      <c r="T57" s="4" t="inlineStr"/>
-      <c r="U57" s="4" t="inlineStr"/>
-      <c r="V57" s="4" t="inlineStr"/>
-      <c r="W57" s="4" t="inlineStr"/>
-      <c r="X57" s="4" t="inlineStr"/>
-      <c r="Y57" s="4" t="inlineStr"/>
-      <c r="Z57" s="4" t="inlineStr"/>
-      <c r="AA57" s="4" t="inlineStr"/>
-      <c r="AB57" s="4" t="inlineStr"/>
-      <c r="AC57" s="4" t="inlineStr"/>
-      <c r="AD57" s="4" t="inlineStr"/>
-      <c r="AE57" s="4" t="inlineStr"/>
-      <c r="AF57" s="4" t="inlineStr"/>
-      <c r="AG57" s="4" t="inlineStr"/>
-      <c r="AH57" s="4" t="inlineStr"/>
-      <c r="AI57" s="4" t="inlineStr"/>
-      <c r="AJ57" s="4" t="inlineStr"/>
+      <c r="L57" s="4" t="inlineStr">
+        <is>
+          <t>03.737.188/0001-43</t>
+        </is>
+      </c>
+      <c r="M57" s="4" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="N57" s="4" t="inlineStr">
+        <is>
+          <t>Moderado</t>
+        </is>
+      </c>
+      <c r="O57" s="4" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="P57" s="4" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="Q57" s="4" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="R57" s="4" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="S57" s="4" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="T57" s="4" t="inlineStr">
+        <is>
+          <t>D+0 (du)</t>
+        </is>
+      </c>
+      <c r="U57" s="4" t="inlineStr">
+        <is>
+          <t>D+1 (du)</t>
+        </is>
+      </c>
+      <c r="V57" s="4" t="inlineStr">
+        <is>
+          <t>D+03 (du)</t>
+        </is>
+      </c>
+      <c r="W57" s="4" t="inlineStr">
+        <is>
+          <t>70% CDI + 30% IBOV</t>
+        </is>
+      </c>
+      <c r="X57" s="4" t="inlineStr">
+        <is>
+          <t>Multimercado</t>
+        </is>
+      </c>
+      <c r="Y57" s="4" t="inlineStr">
+        <is>
+          <t>Aberto para captação</t>
+        </is>
+      </c>
+      <c r="Z57" s="4" t="inlineStr">
+        <is>
+          <t>LONGO PRAZO</t>
+        </is>
+      </c>
+      <c r="AA57" s="4" t="inlineStr">
+        <is>
+          <t>GERAL</t>
+        </is>
+      </c>
+      <c r="AB57" s="4" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AC57" s="4" t="inlineStr">
+        <is>
+          <t>16h00</t>
+        </is>
+      </c>
+      <c r="AD57" s="4" t="inlineStr">
+        <is>
+          <t>Sim · Automatico · 100%</t>
+        </is>
+      </c>
+      <c r="AE57" s="4" t="inlineStr">
+        <is>
+          <t>AUTOMATICO</t>
+        </is>
+      </c>
+      <c r="AF57" s="4" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="AG57" s="4" t="inlineStr">
+        <is>
+          <t>["GOV", "Institucional", "Pessoa Física", "PJ Atacado", "PJ Varejo", "Private", "RPPS"]</t>
+        </is>
+      </c>
+      <c r="AH57" s="4" t="inlineStr">
+        <is>
+          <t>["GOV", "Institucional", "Pessoa Física", "PJ Atacado", "PJ Varejo", "Private", "RPPS"]</t>
+        </is>
+      </c>
+      <c r="AI57" s="4" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="AJ57" s="4" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
       <c r="AK57" s="4" t="inlineStr"/>
-      <c r="AL57" s="4" t="inlineStr"/>
-      <c r="AM57" s="4" t="inlineStr"/>
-      <c r="AN57" s="4" t="inlineStr"/>
-      <c r="AO57" s="4" t="inlineStr"/>
-      <c r="AP57" s="4" t="inlineStr"/>
-      <c r="AQ57" s="4" t="inlineStr"/>
-      <c r="AR57" s="4" t="inlineStr"/>
-      <c r="AS57" s="4" t="inlineStr"/>
-      <c r="AT57" s="4" t="inlineStr"/>
-      <c r="AU57" s="4" t="inlineStr"/>
-      <c r="AV57" s="4" t="inlineStr"/>
-      <c r="AW57" s="4" t="inlineStr"/>
+      <c r="AL57" s="4" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+      <c r="AM57" s="4" t="inlineStr">
+        <is>
+          <t>CAIXA RV 30 FUNDO DE INVESTIMENTO FINANCEIRO MULTIMERCADO LONGO PRAZO - RESPONSABILIDADE LIMITADA</t>
+        </is>
+      </c>
+      <c r="AN57" s="4" t="inlineStr">
+        <is>
+          <t>A contagem para conversão de cotas e pagamento do resgate é feita em dias úteis, conforme estabelecido no Regulamento do Fundo. Este Fundo está adaptado às normas vigentes para RPPS (Regimes Próprios de Previdência Social).</t>
+        </is>
+      </c>
+      <c r="AO57" s="4" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_0082.pdf</t>
+        </is>
+      </c>
+      <c r="AP57" s="4" t="inlineStr">
+        <is>
+          <t>http://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_0082.pdf</t>
+        </is>
+      </c>
+      <c r="AQ57" s="4" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_0082.pdf</t>
+        </is>
+      </c>
+      <c r="AR57" s="4" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/FR_0082.pdf</t>
+        </is>
+      </c>
+      <c r="AS57" s="4" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_82.pdf</t>
+        </is>
+      </c>
+      <c r="AT57" s="4" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_82.pdf</t>
+        </is>
+      </c>
+      <c r="AU57" s="4" t="inlineStr">
+        <is>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-termos-adesao/TA_0082.pdf</t>
+        </is>
+      </c>
+      <c r="AV57" s="4" t="inlineStr">
+        <is>
+          <t>http://www.caixa.gov.br/caixa-asset/sumario-remuneracao/Documents/sumarios/0082-SUMARIO.pdf</t>
+        </is>
+      </c>
+      <c r="AW57" s="4" t="inlineStr">
+        <is>
+          <t>https://web.microsoftstream.com/video/86aa0100-d5af-4db2-9f67-441255924e4e?channelId=772517ff-88ae-4298-88f2-3ed5a5893c3e</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -17224,15 +17514,19 @@
           <t>PF</t>
         </is>
       </c>
-      <c r="K73" s="4" t="inlineStr"/>
+      <c r="K73" s="4" t="inlineStr">
+        <is>
+          <t>http://www.caixa.gov.br/fundos-investimento/multimercado/estrategia-livre-mm-lp/Paginas/default.aspx</t>
+        </is>
+      </c>
       <c r="L73" s="4" t="inlineStr">
         <is>
-          <t>35.536.472/0001-48</t>
+          <t>34.660.333/0001-69</t>
         </is>
       </c>
       <c r="M73" s="4" t="inlineStr">
         <is>
-          <t>6479</t>
+          <t>6440</t>
         </is>
       </c>
       <c r="N73" s="4" t="inlineStr">
@@ -17242,7 +17536,7 @@
       </c>
       <c r="O73" s="4" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="P73" s="4" t="inlineStr">
@@ -17330,8 +17624,16 @@
           <t>100.0</t>
         </is>
       </c>
-      <c r="AG73" s="4" t="inlineStr"/>
-      <c r="AH73" s="4" t="inlineStr"/>
+      <c r="AG73" s="4" t="inlineStr">
+        <is>
+          <t>["Pessoa Física", "Private"]</t>
+        </is>
+      </c>
+      <c r="AH73" s="4" t="inlineStr">
+        <is>
+          <t>["Pessoa Física", "Private"]</t>
+        </is>
+      </c>
       <c r="AI73" s="4" t="inlineStr">
         <is>
           <t>Não</t>
@@ -17350,52 +17652,48 @@
       </c>
       <c r="AM73" s="4" t="inlineStr">
         <is>
-          <t>CAIXA FUNCIONÁRIOS ESTRATÉGIA LIVRE FUNDO DE INVESTIMENTO EM COTAS DE CLASSE DE FUNDO DE INVESTIMENTO FINANCEIRO MULTIMERCADO LONGO PRAZO - RESPONSABI</t>
-        </is>
-      </c>
-      <c r="AN73" s="4" t="inlineStr">
-        <is>
-          <t>Fundo destinado a Funcionários e aposentados da Caixa Econômica Federal. Disponível para aplicação somente via conta corrente marcada como conta-salário empregado CAIXA.</t>
-        </is>
-      </c>
+          <t>CAIXA ESTRATÉGIA LIVRE FUNDO DE INVESTIMENTO EM COTAS DE CLASSE DE FUNDO DE INVESTIMENTO FINANCEIRO MULTIMERCADO LONGO PRAZO - RESPONSABILIDADE LIMITA</t>
+        </is>
+      </c>
+      <c r="AN73" s="4" t="inlineStr"/>
       <c r="AO73" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_6479.pdf</t>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-laminas/LA_6440.pdf</t>
         </is>
       </c>
       <c r="AP73" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_6479.pdf</t>
+          <t>https://www.caixa.gov.br/downloads/aplicacao-financeira-regulamentos/RG_6440.pdf</t>
         </is>
       </c>
       <c r="AQ73" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_6479.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-inf-com/FIC_6440.pdf</t>
         </is>
       </c>
       <c r="AR73" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/COM_6479.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-comunicado-aos-cotistas/COM_6440.pdf</t>
         </is>
       </c>
       <c r="AS73" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_6479.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-carta-mensal/CM_6440.pdf</t>
         </is>
       </c>
       <c r="AT73" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_6479.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-laminas-comerciais/LAC_6440.pdf</t>
         </is>
       </c>
       <c r="AU73" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-termos-adesao/TA_6479.pdf</t>
+          <t>https://www.caixa.gov.br/Downloads/aplicacao-financeira-termos-adesao/TA_6440.pdf</t>
         </is>
       </c>
       <c r="AV73" s="4" t="inlineStr">
         <is>
-          <t>https://www.caixa.gov.br/caixa-asset/sumario-remuneracao/Documents/sumarios/6479-SUMARIO.pdf</t>
+          <t>https://www.caixa.gov.br/caixa-asset/sumario-remuneracao/Documents/sumarios/6440-SUMARIO.pdf</t>
         </is>
       </c>
       <c r="AW73" s="4" t="inlineStr"/>
